--- a/catalogs/Saturn-каталог-полный-техданные.xlsx
+++ b/catalogs/Saturn-каталог-полный-техданные.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Статус" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Каталог'!$A$1:$M$99</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Каталог'!$A$1:$M$100</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -506,7 +506,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M99"/>
+  <dimension ref="A1:M100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -1140,7 +1140,11 @@
           <t>от 112 ₽</t>
         </is>
       </c>
-      <c r="E10" s="3" t="inlineStr"/>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>800 кг</t>
+        </is>
+      </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
           <t>Гранулированное бесхлорное удобрение для овощных и плодово-ягодных культур.</t>
@@ -1199,7 +1203,11 @@
           <t>от 96 ₽</t>
         </is>
       </c>
-      <c r="E11" s="7" t="inlineStr"/>
+      <c r="E11" s="7" t="inlineStr">
+        <is>
+          <t>800 кг</t>
+        </is>
+      </c>
       <c r="F11" s="7" t="inlineStr">
         <is>
           <t>Гранулированное удобрение для густого газона и ярко-зелёной окраски травы.</t>
@@ -1258,7 +1266,11 @@
           <t>от 106 ₽</t>
         </is>
       </c>
-      <c r="E12" s="3" t="inlineStr"/>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>800 кг</t>
+        </is>
+      </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
           <t>Осеннее фосфорно-калийное удобрение для подготовки растений к стрессам.</t>
@@ -1376,7 +1388,11 @@
           <t>от 110 ₽</t>
         </is>
       </c>
-      <c r="E14" s="3" t="inlineStr"/>
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t>800 кг</t>
+        </is>
+      </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
           <t>Специализированное удобрение для клубнеобразования и повышения качества картофеля.</t>
@@ -1558,7 +1574,7 @@
       </c>
       <c r="D17" s="8" t="inlineStr">
         <is>
-          <t>от 645.7 ₽</t>
+          <t>от 585 ₽</t>
         </is>
       </c>
       <c r="E17" s="7" t="inlineStr">
@@ -1621,7 +1637,7 @@
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>от 724.5 ₽</t>
+          <t>от 700 ₽</t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
@@ -1684,7 +1700,7 @@
       </c>
       <c r="D19" s="8" t="inlineStr">
         <is>
-          <t>от 651 ₽</t>
+          <t>от 595 ₽</t>
         </is>
       </c>
       <c r="E19" s="7" t="inlineStr">
@@ -1747,7 +1763,7 @@
       </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
-          <t>от 651 ₽</t>
+          <t>Цена по запросу</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr"/>
@@ -1806,7 +1822,7 @@
       </c>
       <c r="D21" s="8" t="inlineStr">
         <is>
-          <t>от 409.5 ₽</t>
+          <t>от 315 ₽</t>
         </is>
       </c>
       <c r="E21" s="7" t="inlineStr">
@@ -1869,7 +1885,7 @@
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>от 577.5 ₽</t>
+          <t>от 535 ₽</t>
         </is>
       </c>
       <c r="E22" s="3" t="inlineStr">
@@ -1932,7 +1948,7 @@
       </c>
       <c r="D23" s="8" t="inlineStr">
         <is>
-          <t>от 332.5 ₽</t>
+          <t>от 315 ₽</t>
         </is>
       </c>
       <c r="E23" s="7" t="inlineStr">
@@ -1995,7 +2011,7 @@
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>от 490 ₽</t>
+          <t>от 450 ₽</t>
         </is>
       </c>
       <c r="E24" s="3" t="inlineStr"/>
@@ -2054,7 +2070,7 @@
       </c>
       <c r="D25" s="8" t="inlineStr">
         <is>
-          <t>от 760 ₽</t>
+          <t>от 635 ₽</t>
         </is>
       </c>
       <c r="E25" s="7" t="inlineStr"/>
@@ -2070,7 +2086,7 @@
       </c>
       <c r="H25" s="7" t="inlineStr">
         <is>
-          <t>0,5 л/га, 1–2 обработки (до 1 л/га при низком содержании бора). Рабочий раствор 100–300 л/га</t>
+          <t>0,5 - 1,0  л/га, 1–2 обработки (до 1 л/га при низком содержании бора). Рабочий раствор 100–300 л/га</t>
         </is>
       </c>
       <c r="I25" s="7" t="inlineStr">
@@ -2113,7 +2129,7 @@
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>от 728 ₽</t>
+          <t>от 500 ₽</t>
         </is>
       </c>
       <c r="E26" s="3" t="inlineStr"/>
@@ -2172,7 +2188,7 @@
       </c>
       <c r="D27" s="8" t="inlineStr">
         <is>
-          <t>от 430 ₽</t>
+          <t>от 400 ₽</t>
         </is>
       </c>
       <c r="E27" s="7" t="inlineStr"/>
@@ -2231,7 +2247,7 @@
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>от 465 ₽</t>
+          <t>от 545 ₽</t>
         </is>
       </c>
       <c r="E28" s="3" t="inlineStr"/>
@@ -2247,7 +2263,7 @@
       </c>
       <c r="H28" s="3" t="inlineStr">
         <is>
-          <t>0,5–1,0 л/га. Рабочий раствор 100–300 л/га</t>
+          <t>0,2–1,0 л/га. Рабочий раствор 100–300 л/га</t>
         </is>
       </c>
       <c r="I28" s="3" t="inlineStr">
@@ -2294,7 +2310,7 @@
       </c>
       <c r="D29" s="8" t="inlineStr">
         <is>
-          <t>от 1290 ₽</t>
+          <t>от 1470 ₽</t>
         </is>
       </c>
       <c r="E29" s="7" t="inlineStr">
@@ -2357,7 +2373,7 @@
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>от 650 ₽</t>
+          <t>от 685 ₽</t>
         </is>
       </c>
       <c r="E30" s="3" t="inlineStr">
@@ -2420,7 +2436,7 @@
       </c>
       <c r="D31" s="8" t="inlineStr">
         <is>
-          <t>от 653 ₽</t>
+          <t>от 670 ₽</t>
         </is>
       </c>
       <c r="E31" s="7" t="inlineStr">
@@ -2483,7 +2499,7 @@
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>от 520 ₽</t>
+          <t>от 455 ₽</t>
         </is>
       </c>
       <c r="E32" s="3" t="inlineStr">
@@ -2546,7 +2562,7 @@
       </c>
       <c r="D33" s="8" t="inlineStr">
         <is>
-          <t>от 605 ₽</t>
+          <t>от 510 ₽</t>
         </is>
       </c>
       <c r="E33" s="7" t="inlineStr">
@@ -2609,7 +2625,7 @@
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>от 1290 ₽</t>
+          <t>Цена по запросу</t>
         </is>
       </c>
       <c r="E34" s="3" t="inlineStr">
@@ -2672,7 +2688,7 @@
       </c>
       <c r="D35" s="8" t="inlineStr">
         <is>
-          <t>от 695 ₽</t>
+          <t>от 800 ₽</t>
         </is>
       </c>
       <c r="E35" s="7" t="inlineStr">
@@ -2735,7 +2751,7 @@
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>от 1020 ₽</t>
+          <t>от 1245 ₽</t>
         </is>
       </c>
       <c r="E36" s="3" t="inlineStr">
@@ -2999,7 +3015,7 @@
       </c>
       <c r="H40" s="3" t="inlineStr">
         <is>
-          <t>0,5 л/га листовая подкормка (рапс — фазы розетка, стеблевание, бутонизация)</t>
+          <t>0,3-1,5 л/га листовая подкормка (рапс — фазы розетка, стеблевание, бутонизация)</t>
         </is>
       </c>
       <c r="I40" s="3" t="inlineStr">
@@ -3117,7 +3133,7 @@
       </c>
       <c r="H42" s="3" t="inlineStr">
         <is>
-          <t>0,43–1,0 л/га листовая подкормка</t>
+          <t>0,3–1,5 л/га листовая подкормка</t>
         </is>
       </c>
       <c r="I42" s="3" t="inlineStr">
@@ -6265,8 +6281,59 @@
       </c>
       <c r="M99" s="10" t="inlineStr"/>
     </row>
+    <row r="100" ht="80" customHeight="1">
+      <c r="A100" s="2" t="inlineStr">
+        <is>
+          <t>Волски Аминатор</t>
+        </is>
+      </c>
+      <c r="B100" s="3" t="inlineStr">
+        <is>
+          <t>Волски Биохим</t>
+        </is>
+      </c>
+      <c r="C100" s="3" t="inlineStr">
+        <is>
+          <t>Листовые подкормки</t>
+        </is>
+      </c>
+      <c r="D100" s="4" t="inlineStr">
+        <is>
+          <t>от 900 ₽</t>
+        </is>
+      </c>
+      <c r="E100" s="3" t="inlineStr">
+        <is>
+          <t>раствор</t>
+        </is>
+      </c>
+      <c r="F100" s="3" t="inlineStr">
+        <is>
+          <t>Комплекс аминокислот нового поколения для быстрого снятия стресса во время засухи и активации роста</t>
+        </is>
+      </c>
+      <c r="G100" s="3" t="inlineStr"/>
+      <c r="H100" s="3" t="inlineStr">
+        <is>
+          <t>0,5 л/га</t>
+        </is>
+      </c>
+      <c r="I100" s="3" t="inlineStr"/>
+      <c r="J100" s="3" t="inlineStr"/>
+      <c r="K100" s="3" t="inlineStr"/>
+      <c r="L100" s="3" t="inlineStr">
+        <is>
+          <t>Данные заказчика, 2026-09-25</t>
+        </is>
+      </c>
+      <c r="M100" s="5" t="inlineStr">
+        <is>
+          <t>нормы</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M99"/>
+  <autoFilter ref="A1:M100"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -6372,7 +6439,7 @@
       </c>
       <c r="B9" s="13" t="inlineStr">
         <is>
-          <t>24 позиций</t>
+          <t>25 позиций</t>
         </is>
       </c>
     </row>
@@ -6468,7 +6535,7 @@
       </c>
       <c r="B17" s="13" t="inlineStr">
         <is>
-          <t>98 позиций</t>
+          <t>99 позиций</t>
         </is>
       </c>
     </row>

--- a/catalogs/Saturn-каталог-полный-техданные.xlsx
+++ b/catalogs/Saturn-каталог-полный-техданные.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Каталог" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Статус" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Каталог" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Статус" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Каталог'!$A$1:$M$100</definedName>

--- a/catalogs/Saturn-каталог-полный-техданные.xlsx
+++ b/catalogs/Saturn-каталог-полный-техданные.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Каталог" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Статус" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Каталог" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Статус" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Каталог'!$A$1:$M$100</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Каталог'!$A$1:$M$99</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -506,7 +506,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M100"/>
+  <dimension ref="A1:M99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -1140,11 +1140,7 @@
           <t>от 112 ₽</t>
         </is>
       </c>
-      <c r="E10" s="3" t="inlineStr">
-        <is>
-          <t>800 кг</t>
-        </is>
-      </c>
+      <c r="E10" s="3" t="inlineStr"/>
       <c r="F10" s="3" t="inlineStr">
         <is>
           <t>Гранулированное бесхлорное удобрение для овощных и плодово-ягодных культур.</t>
@@ -1203,11 +1199,7 @@
           <t>от 96 ₽</t>
         </is>
       </c>
-      <c r="E11" s="7" t="inlineStr">
-        <is>
-          <t>800 кг</t>
-        </is>
-      </c>
+      <c r="E11" s="7" t="inlineStr"/>
       <c r="F11" s="7" t="inlineStr">
         <is>
           <t>Гранулированное удобрение для густого газона и ярко-зелёной окраски травы.</t>
@@ -1266,11 +1258,7 @@
           <t>от 106 ₽</t>
         </is>
       </c>
-      <c r="E12" s="3" t="inlineStr">
-        <is>
-          <t>800 кг</t>
-        </is>
-      </c>
+      <c r="E12" s="3" t="inlineStr"/>
       <c r="F12" s="3" t="inlineStr">
         <is>
           <t>Осеннее фосфорно-калийное удобрение для подготовки растений к стрессам.</t>
@@ -1388,11 +1376,7 @@
           <t>от 110 ₽</t>
         </is>
       </c>
-      <c r="E14" s="3" t="inlineStr">
-        <is>
-          <t>800 кг</t>
-        </is>
-      </c>
+      <c r="E14" s="3" t="inlineStr"/>
       <c r="F14" s="3" t="inlineStr">
         <is>
           <t>Специализированное удобрение для клубнеобразования и повышения качества картофеля.</t>
@@ -1574,7 +1558,7 @@
       </c>
       <c r="D17" s="8" t="inlineStr">
         <is>
-          <t>от 585 ₽</t>
+          <t>от 645.7 ₽</t>
         </is>
       </c>
       <c r="E17" s="7" t="inlineStr">
@@ -1637,7 +1621,7 @@
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>от 700 ₽</t>
+          <t>от 724.5 ₽</t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
@@ -1700,7 +1684,7 @@
       </c>
       <c r="D19" s="8" t="inlineStr">
         <is>
-          <t>от 595 ₽</t>
+          <t>от 651 ₽</t>
         </is>
       </c>
       <c r="E19" s="7" t="inlineStr">
@@ -1763,7 +1747,7 @@
       </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
-          <t>Цена по запросу</t>
+          <t>от 651 ₽</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr"/>
@@ -1822,7 +1806,7 @@
       </c>
       <c r="D21" s="8" t="inlineStr">
         <is>
-          <t>от 315 ₽</t>
+          <t>от 409.5 ₽</t>
         </is>
       </c>
       <c r="E21" s="7" t="inlineStr">
@@ -1885,7 +1869,7 @@
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>от 535 ₽</t>
+          <t>от 577.5 ₽</t>
         </is>
       </c>
       <c r="E22" s="3" t="inlineStr">
@@ -1948,7 +1932,7 @@
       </c>
       <c r="D23" s="8" t="inlineStr">
         <is>
-          <t>от 315 ₽</t>
+          <t>от 332.5 ₽</t>
         </is>
       </c>
       <c r="E23" s="7" t="inlineStr">
@@ -2011,7 +1995,7 @@
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>от 450 ₽</t>
+          <t>от 490 ₽</t>
         </is>
       </c>
       <c r="E24" s="3" t="inlineStr"/>
@@ -2070,7 +2054,7 @@
       </c>
       <c r="D25" s="8" t="inlineStr">
         <is>
-          <t>от 635 ₽</t>
+          <t>от 760 ₽</t>
         </is>
       </c>
       <c r="E25" s="7" t="inlineStr"/>
@@ -2086,7 +2070,7 @@
       </c>
       <c r="H25" s="7" t="inlineStr">
         <is>
-          <t>0,5 - 1,0  л/га, 1–2 обработки (до 1 л/га при низком содержании бора). Рабочий раствор 100–300 л/га</t>
+          <t>0,5 л/га, 1–2 обработки (до 1 л/га при низком содержании бора). Рабочий раствор 100–300 л/га</t>
         </is>
       </c>
       <c r="I25" s="7" t="inlineStr">
@@ -2129,7 +2113,7 @@
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>от 500 ₽</t>
+          <t>от 728 ₽</t>
         </is>
       </c>
       <c r="E26" s="3" t="inlineStr"/>
@@ -2188,7 +2172,7 @@
       </c>
       <c r="D27" s="8" t="inlineStr">
         <is>
-          <t>от 400 ₽</t>
+          <t>от 430 ₽</t>
         </is>
       </c>
       <c r="E27" s="7" t="inlineStr"/>
@@ -2247,7 +2231,7 @@
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>от 545 ₽</t>
+          <t>от 465 ₽</t>
         </is>
       </c>
       <c r="E28" s="3" t="inlineStr"/>
@@ -2263,7 +2247,7 @@
       </c>
       <c r="H28" s="3" t="inlineStr">
         <is>
-          <t>0,2–1,0 л/га. Рабочий раствор 100–300 л/га</t>
+          <t>0,5–1,0 л/га. Рабочий раствор 100–300 л/га</t>
         </is>
       </c>
       <c r="I28" s="3" t="inlineStr">
@@ -2310,7 +2294,7 @@
       </c>
       <c r="D29" s="8" t="inlineStr">
         <is>
-          <t>от 1470 ₽</t>
+          <t>от 1290 ₽</t>
         </is>
       </c>
       <c r="E29" s="7" t="inlineStr">
@@ -2373,7 +2357,7 @@
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>от 685 ₽</t>
+          <t>от 650 ₽</t>
         </is>
       </c>
       <c r="E30" s="3" t="inlineStr">
@@ -2436,7 +2420,7 @@
       </c>
       <c r="D31" s="8" t="inlineStr">
         <is>
-          <t>от 670 ₽</t>
+          <t>от 653 ₽</t>
         </is>
       </c>
       <c r="E31" s="7" t="inlineStr">
@@ -2499,7 +2483,7 @@
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>от 455 ₽</t>
+          <t>от 520 ₽</t>
         </is>
       </c>
       <c r="E32" s="3" t="inlineStr">
@@ -2562,7 +2546,7 @@
       </c>
       <c r="D33" s="8" t="inlineStr">
         <is>
-          <t>от 510 ₽</t>
+          <t>от 605 ₽</t>
         </is>
       </c>
       <c r="E33" s="7" t="inlineStr">
@@ -2625,7 +2609,7 @@
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>Цена по запросу</t>
+          <t>от 1290 ₽</t>
         </is>
       </c>
       <c r="E34" s="3" t="inlineStr">
@@ -2688,7 +2672,7 @@
       </c>
       <c r="D35" s="8" t="inlineStr">
         <is>
-          <t>от 800 ₽</t>
+          <t>от 695 ₽</t>
         </is>
       </c>
       <c r="E35" s="7" t="inlineStr">
@@ -2751,7 +2735,7 @@
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>от 1245 ₽</t>
+          <t>от 1020 ₽</t>
         </is>
       </c>
       <c r="E36" s="3" t="inlineStr">
@@ -3015,7 +2999,7 @@
       </c>
       <c r="H40" s="3" t="inlineStr">
         <is>
-          <t>0,3-1,5 л/га листовая подкормка (рапс — фазы розетка, стеблевание, бутонизация)</t>
+          <t>0,5 л/га листовая подкормка (рапс — фазы розетка, стеблевание, бутонизация)</t>
         </is>
       </c>
       <c r="I40" s="3" t="inlineStr">
@@ -3133,7 +3117,7 @@
       </c>
       <c r="H42" s="3" t="inlineStr">
         <is>
-          <t>0,3–1,5 л/га листовая подкормка</t>
+          <t>0,43–1,0 л/га листовая подкормка</t>
         </is>
       </c>
       <c r="I42" s="3" t="inlineStr">
@@ -6281,59 +6265,8 @@
       </c>
       <c r="M99" s="10" t="inlineStr"/>
     </row>
-    <row r="100" ht="80" customHeight="1">
-      <c r="A100" s="2" t="inlineStr">
-        <is>
-          <t>Волски Аминатор</t>
-        </is>
-      </c>
-      <c r="B100" s="3" t="inlineStr">
-        <is>
-          <t>Волски Биохим</t>
-        </is>
-      </c>
-      <c r="C100" s="3" t="inlineStr">
-        <is>
-          <t>Листовые подкормки</t>
-        </is>
-      </c>
-      <c r="D100" s="4" t="inlineStr">
-        <is>
-          <t>от 900 ₽</t>
-        </is>
-      </c>
-      <c r="E100" s="3" t="inlineStr">
-        <is>
-          <t>раствор</t>
-        </is>
-      </c>
-      <c r="F100" s="3" t="inlineStr">
-        <is>
-          <t>Комплекс аминокислот нового поколения для быстрого снятия стресса во время засухи и активации роста</t>
-        </is>
-      </c>
-      <c r="G100" s="3" t="inlineStr"/>
-      <c r="H100" s="3" t="inlineStr">
-        <is>
-          <t>0,5 л/га</t>
-        </is>
-      </c>
-      <c r="I100" s="3" t="inlineStr"/>
-      <c r="J100" s="3" t="inlineStr"/>
-      <c r="K100" s="3" t="inlineStr"/>
-      <c r="L100" s="3" t="inlineStr">
-        <is>
-          <t>Данные заказчика, 2026-09-25</t>
-        </is>
-      </c>
-      <c r="M100" s="5" t="inlineStr">
-        <is>
-          <t>нормы</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:M100"/>
+  <autoFilter ref="A1:M99"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -6439,7 +6372,7 @@
       </c>
       <c r="B9" s="13" t="inlineStr">
         <is>
-          <t>25 позиций</t>
+          <t>24 позиций</t>
         </is>
       </c>
     </row>
@@ -6535,7 +6468,7 @@
       </c>
       <c r="B17" s="13" t="inlineStr">
         <is>
-          <t>99 позиций</t>
+          <t>98 позиций</t>
         </is>
       </c>
     </row>
